--- a/artfynd/A 24880-2026 artfynd.xlsx
+++ b/artfynd/A 24880-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134084589</v>
       </c>
       <c r="B2" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>134084569</v>
       </c>
       <c r="B3" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24880-2026 artfynd.xlsx
+++ b/artfynd/A 24880-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134084589</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>134084569</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24880-2026 artfynd.xlsx
+++ b/artfynd/A 24880-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134084589</v>
+        <v>73490524</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kärret, Kärret, Nrk</t>
+          <t>Filipshyttan 334, sydväst om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498725</v>
+        <v>498824</v>
       </c>
       <c r="R2" t="n">
-        <v>6576240</v>
+        <v>6576273</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2018-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En fruktkropp vid foten av en gammal tallöverståndare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,18 +769,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -794,7 +810,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134084648</v>
+        <v>134084589</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +926,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärret, Kärret, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498693</v>
+        <v>498725</v>
       </c>
       <c r="R4" t="n">
-        <v>6576229</v>
+        <v>6576240</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134084827</v>
+        <v>134084648</v>
       </c>
       <c r="B5" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1038,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498704</v>
+        <v>498693</v>
       </c>
       <c r="R5" t="n">
-        <v>6576151</v>
+        <v>6576229</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,6 +1131,220 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134084799</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kärret, Kärret, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498687</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6576150</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134084827</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kärret, Kärret, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498704</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6576151</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24880-2026 artfynd.xlsx
+++ b/artfynd/A 24880-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73490524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134084569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134084589</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134084648</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134084799</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,8 +1375,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134084827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>